--- a/naver-place-crawler/results_hair/계양구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/계양구_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V322"/>
+  <dimension ref="A1:V378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28265,29 +28265,25 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>머리염색</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>오땡큐 임학점</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>malia98@naver.com</t>
-        </is>
-      </c>
+          <t>은영헤어</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t>032-221-7672</t>
+          <t>032-545-0050</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 임학서로27번길 1 1층</t>
+          <t>인천광역시 계양구 당미길 12 당미길 1층상가 은영헤어</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -28327,13 +28323,13 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="Q301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R301" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
@@ -28342,12 +28338,12 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>1238483300</t>
+          <t>1456178352</t>
         </is>
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1238483300</t>
+          <t>https://m.place.naver.com/place/1456178352</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
@@ -28359,30 +28355,34 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>머리염색</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>구피염색방계산점</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr"/>
+          <t>더보보헤어 효성점</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>0116853923@naver.com</t>
+        </is>
+      </c>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>032-546-5040</t>
+          <t>0507-1415-3922</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계산시장길 21 1층</t>
+          <t>인천광역시 계양구 마장로544번길 10 디오아제 상가 2층 B2-207</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/thebobohair</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -28392,7 +28392,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -28413,17 +28413,17 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P302" t="n">
-        <v>28</v>
+        <v>272</v>
       </c>
       <c r="Q302" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R302" t="n">
-        <v>28</v>
+        <v>309</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
@@ -28432,51 +28432,51 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>33253220</t>
+          <t>2011537843</t>
         </is>
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33253220</t>
+          <t>https://m.place.naver.com/place/2011537843</t>
         </is>
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>땡글하개</t>
+          <t>로브맨즈헤어</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>dde_ngle@naver.com</t>
+          <t>woodong37@naver.com</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>0507-1390-7630</t>
+          <t>0507-1460-2439</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 안남로519번길 4 101동 상가1층 106호</t>
+          <t>인천광역시 계양구 마장로544번길 10 판매시설동 2층 B2-215호</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dde_ngle</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -28486,7 +28486,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -28507,17 +28507,17 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P303" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="Q303" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R303" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -28526,51 +28526,47 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>1276697582</t>
+          <t>2039961875</t>
         </is>
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1276697582</t>
+          <t>https://m.place.naver.com/place/2039961875</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>온댕</t>
+          <t>라미살롱</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ondangg@naver.com</t>
+          <t>laisydesign@naver.com</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>0507-1446-7832</t>
-        </is>
-      </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 주부토로 426</t>
+          <t>인천광역시 계양구 아나지로 390-1 1층</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/l_on_daeng</t>
+          <t>https://www.instagram.com/ramisalon_rambo</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -28605,13 +28601,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="Q304" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R304" t="n">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -28620,46 +28616,38 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>1908396752</t>
+          <t>1501870775</t>
         </is>
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1908396752</t>
+          <t>https://m.place.naver.com/place/1501870775</t>
         </is>
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>도그의 품격</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>adp4929@naver.com</t>
-        </is>
-      </c>
+          <t>헤어짱</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>0507-1360-2840</t>
-        </is>
-      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 안남로554번길 8 1층</t>
+          <t>인천광역시 계양구 병방시장로 32</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -28699,13 +28687,13 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="Q305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R305" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -28714,47 +28702,51 @@
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>1783582750</t>
+          <t>1096904114</t>
         </is>
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1783582750</t>
+          <t>https://m.place.naver.com/place/1096904114</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>아우어패밀리 인천본점</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr"/>
+          <t>이지헤어</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>vv911014@naver.com</t>
+        </is>
+      </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>0507-1482-0105</t>
+          <t>032-552-7799</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로1045번길 9-9 지산상가 202호 아우어패밀리</t>
+          <t>인천광역시 계양구 동양로 11 박촌 풍림아이원</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ourfamily._official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -28764,7 +28756,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -28785,17 +28777,17 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P306" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="Q306" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R306" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -28804,51 +28796,51 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>1425555513</t>
+          <t>1968692413</t>
         </is>
       </c>
       <c r="U306" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1425555513</t>
+          <t>https://m.place.naver.com/place/1968692413</t>
         </is>
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>우리동네펫샵</t>
+          <t>헤어1074</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>0131miae@naver.com</t>
+          <t>lovejung0929@naver.com</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>0507-1361-1358</t>
+          <t>032-554-7868</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 용종로 98-1 106호 우리동네펫샵</t>
+          <t>인천광역시 계양구 경명대로 1074 1층</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/0131miae</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -28858,12 +28850,12 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -28879,17 +28871,17 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P307" t="n">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="Q307" t="n">
-        <v>312</v>
+        <v>2</v>
       </c>
       <c r="R307" t="n">
-        <v>423</v>
+        <v>169</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
@@ -28898,47 +28890,51 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>1050496582</t>
+          <t>1294920095</t>
         </is>
       </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050496582</t>
+          <t>https://m.place.naver.com/place/1294920095</t>
         </is>
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>어스펫 1호점</t>
+          <t>살롱 드 감성</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>funjin12@naver.com</t>
+          <t>mctop002@naver.com</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>0507-1442-6696</t>
+        </is>
+      </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장기로 24 102호 어스펫 1호점</t>
+          <t>인천광역시 계양구 봉오대로744번길 12 신진상가 106호</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/funjin12</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -28948,12 +28944,12 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -28969,17 +28965,17 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P308" t="n">
-        <v>37</v>
+        <v>478</v>
       </c>
       <c r="Q308" t="n">
-        <v>257</v>
+        <v>2</v>
       </c>
       <c r="R308" t="n">
-        <v>294</v>
+        <v>480</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -28988,17 +28984,17 @@
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>1776469821</t>
+          <t>1627804015</t>
         </is>
       </c>
       <c r="U308" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776469821</t>
+          <t>https://m.place.naver.com/place/1627804015</t>
         </is>
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -29010,29 +29006,25 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>아스타 펫 살롱</t>
+          <t>봄댕 애견미용실</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>giyang1951@naver.com</t>
+          <t>eulview123@naver.com</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>0507-1381-1983</t>
-        </is>
-      </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 새벌로 140 1층</t>
+          <t>인천광역시 계양구 효서로370번길 11 1층 봄댕</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>http://instagram.com/aster_pet_salon</t>
+          <t>https://www.instagram.com/bomdaeng.pet</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -29067,13 +29059,13 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="Q309" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R309" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -29082,51 +29074,47 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>1548645447</t>
+          <t>2025055644</t>
         </is>
       </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548645447</t>
+          <t>https://m.place.naver.com/place/2025055644</t>
         </is>
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>개예쁨주의</t>
+          <t>마이더스헤어</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>giyang1951@naver.com</t>
+          <t>yhk3230@naver.com</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>0507-1349-7076</t>
-        </is>
-      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로997번길 5 1층 102호(박촌동)</t>
+          <t>인천광역시 계양구 장제로 897</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sj666_1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -29136,7 +29124,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -29157,17 +29145,17 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P310" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="Q310" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R310" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -29176,51 +29164,51 @@
       </c>
       <c r="T310" t="inlineStr">
         <is>
-          <t>1131203259</t>
+          <t>1728872417</t>
         </is>
       </c>
       <c r="U310" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131203259</t>
+          <t>https://m.place.naver.com/place/1728872417</t>
         </is>
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>개팔자상팔자 작전점</t>
+          <t>도도헤어</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>dran77@naver.com</t>
+          <t>skagml1020@naver.com</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>0507-1349-1179</t>
+          <t>032-555-8941</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 효서로 293 1층</t>
+          <t>인천광역시 계양구 당미2길 31</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>http://instagram.com/simyangsu3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -29230,7 +29218,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -29251,17 +29239,17 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P311" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q311" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R311" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -29270,34 +29258,34 @@
       </c>
       <c r="T311" t="inlineStr">
         <is>
-          <t>37765887</t>
+          <t>1602022808</t>
         </is>
       </c>
       <c r="U311" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37765887</t>
+          <t>https://m.place.naver.com/place/1602022808</t>
         </is>
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>엄댕샵</t>
+          <t>소담뷰티헤어</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>jyje0710@naver.com</t>
+          <t>wildspringmoon@naver.com</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -29305,12 +29293,12 @@
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 아나지로307번길 14 1층 엄댕샵</t>
+          <t>인천광역시 계양구 양지로 134 101호</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eomdang_shop/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -29320,7 +29308,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -29341,17 +29329,17 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P312" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="Q312" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R312" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -29360,46 +29348,42 @@
       </c>
       <c r="T312" t="inlineStr">
         <is>
-          <t>1829617868</t>
+          <t>1009688160</t>
         </is>
       </c>
       <c r="U312" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1829617868</t>
+          <t>https://m.place.naver.com/place/1009688160</t>
         </is>
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>개냥아치</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>ojhj1022@naver.com</t>
-        </is>
-      </c>
+          <t>트렌드헤어</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>0507-1352-6270</t>
+          <t>032-541-1220</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계양산로 161 1층 개냥아치</t>
+          <t>인천광역시 계양구 굴재방터길 27 2동 1층 트렌드헤어</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -29439,13 +29423,13 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>30</v>
+        <v>307</v>
       </c>
       <c r="Q313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R313" t="n">
-        <v>33</v>
+        <v>308</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -29454,51 +29438,51 @@
       </c>
       <c r="T313" t="inlineStr">
         <is>
-          <t>1874800081</t>
+          <t>1718024942</t>
         </is>
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874800081</t>
+          <t>https://m.place.naver.com/place/1718024942</t>
         </is>
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>의자</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>비디코리아</t>
+          <t>오늘의 헤어</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>bdkorea21@naver.com</t>
+          <t>me4513@naver.com</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>032-676-2407</t>
+          <t>0507-1353-4513</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 서운산단로8길 20 비디코리아</t>
+          <t>인천광역시 계양구 봉오대로 691 1층</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bdkorea21</t>
+          <t>https://blog.naver.com/me4513</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -29529,17 +29513,17 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P314" t="n">
-        <v>1</v>
+        <v>515</v>
       </c>
       <c r="Q314" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="R314" t="n">
-        <v>55</v>
+        <v>537</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -29548,38 +29532,42 @@
       </c>
       <c r="T314" t="inlineStr">
         <is>
-          <t>11644207</t>
+          <t>1068179479</t>
         </is>
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11644207</t>
+          <t>https://m.place.naver.com/place/1068179479</t>
         </is>
       </c>
       <c r="V314" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>으뜸이용원</t>
+          <t>까망머리</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>070-4195-3223</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 양지로 49</t>
+          <t>인천광역시 계양구 계양산로 171</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -29619,13 +29607,13 @@
         </is>
       </c>
       <c r="P315" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="Q315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R315" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -29634,42 +29622,46 @@
       </c>
       <c r="T315" t="inlineStr">
         <is>
-          <t>21489631</t>
+          <t>1759719549</t>
         </is>
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21489631</t>
+          <t>https://m.place.naver.com/place/1759719549</t>
         </is>
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>동양이발관</t>
+          <t>이지헤어클럽</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>taekstory@naver.com</t>
+          <t>shibao1007@naver.com</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>032-515-7222</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 당미1길 25</t>
+          <t>인천광역시 계양구 장기로14번길 1</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -29709,13 +29701,13 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q316" t="n">
         <v>0</v>
       </c>
       <c r="R316" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -29724,46 +29716,42 @@
       </c>
       <c r="T316" t="inlineStr">
         <is>
-          <t>1089780290</t>
+          <t>19393667</t>
         </is>
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089780290</t>
+          <t>https://m.place.naver.com/place/19393667</t>
         </is>
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>학고을이발관</t>
+          <t>손길 by hair</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>timmy0326@naver.com</t>
+          <t>lea171635@naver.com</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>032-517-9891</t>
-        </is>
-      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 황어로126번길 20</t>
+          <t>인천광역시 계양구 용종로 98 1층</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -29803,13 +29791,13 @@
         </is>
       </c>
       <c r="P317" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>1</v>
-      </c>
       <c r="R317" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -29818,42 +29806,46 @@
       </c>
       <c r="T317" t="inlineStr">
         <is>
-          <t>38367077</t>
+          <t>1611265128</t>
         </is>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38367077</t>
+          <t>https://m.place.naver.com/place/1611265128</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>박촌이발</t>
+          <t>채움헤어</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>dashin2006@naver.com</t>
+          <t>rmfltmdgus@naver.com</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>032-555-3191</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로 1014</t>
+          <t>인천광역시 계양구 계양대로 118 대화상가 105</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -29893,13 +29885,13 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="Q318" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R318" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -29908,51 +29900,51 @@
       </c>
       <c r="T318" t="inlineStr">
         <is>
-          <t>1489911278</t>
+          <t>21082520</t>
         </is>
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489911278</t>
+          <t>https://m.place.naver.com/place/21082520</t>
         </is>
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>시대이용원</t>
+          <t>꼬뉴헤어</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>sacheoncity@naver.com</t>
+          <t>kmjkmj2221@naver.com</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>032-542-6377</t>
+          <t>032-555-7808</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 임학서로 22</t>
+          <t>인천광역시 계양구 주부토로 541 계양프라자 1층 114호 꼬뉴헤어</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gimhyeonjin961</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -29962,7 +29954,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -29983,17 +29975,17 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P319" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q319" t="n">
         <v>5</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
-        <v>5</v>
+        <v>138</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -30002,46 +29994,46 @@
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>19406831</t>
+          <t>1847914669</t>
         </is>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19406831</t>
+          <t>https://m.place.naver.com/place/1847914669</t>
         </is>
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>열린시각이용원</t>
+          <t>리본미용실</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>hnewskr@naver.com</t>
+          <t>baekjeun@naver.com</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>032-512-3140</t>
+          <t>032-547-7766</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 황어로115번길 10 신동아아파트 상가 105호</t>
+          <t>인천광역시 계양구 계양문화로 44</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -30081,13 +30073,13 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>254</v>
+        <v>17</v>
       </c>
       <c r="Q320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R320" t="n">
-        <v>254</v>
+        <v>18</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
@@ -30096,46 +30088,46 @@
       </c>
       <c r="T320" t="inlineStr">
         <is>
-          <t>1584803012</t>
+          <t>16668519</t>
         </is>
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1584803012</t>
+          <t>https://m.place.naver.com/place/16668519</t>
         </is>
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>애영이용원</t>
+          <t>미르헤어 3호점</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>swings81@naver.com</t>
+          <t>wkaorlfdl@naver.com</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>032-542-2882</t>
+          <t>032-546-1608</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 임학동로56번길 16</t>
+          <t>인천광역시 계양구 동양로 100-2 구두수선대</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -30175,13 +30167,13 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="Q321" t="n">
         <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
@@ -30190,46 +30182,46 @@
       </c>
       <c r="T321" t="inlineStr">
         <is>
-          <t>38379600</t>
+          <t>1440331716</t>
         </is>
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38379600</t>
+          <t>https://m.place.naver.com/place/1440331716</t>
         </is>
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>모조바버샵</t>
+          <t>더샵헤어</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>ssmnc@naver.com</t>
+          <t>jw6486@naver.com</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>0507-1326-4961</t>
+          <t>0507-1332-9870</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 아나지로 332 카이저팰리스 101동상가116호 (인천광역시 계양구 작전동 392-1 카이저팰리스 101동상가 1층116호)</t>
+          <t>인천광역시 계양구 장제로 719-17 일신빌딩</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -30269,32 +30261,5204 @@
         </is>
       </c>
       <c r="P322" t="n">
+        <v>699</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>11</v>
+      </c>
+      <c r="R322" t="n">
+        <v>710</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>1131817986</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1131817986</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>비앤온헤어</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>seungyeon706@naver.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>070-7543-2334</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 계양대로119번길 1 로비층 비앤온</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seungyeon706</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>616</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>60</v>
+      </c>
+      <c r="R323" t="n">
+        <v>676</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>1932317243</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932317243</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>베스트헤어</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ttlsunhwa@naver.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>032-555-7747</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학안로28번길 4</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>0</v>
+      </c>
+      <c r="R324" t="n">
+        <v>43</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>1108828934</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1108828934</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>리치헤어</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>behyebbi@naver.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>032-552-5277</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 양지로 137</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>0</v>
+      </c>
+      <c r="R325" t="n">
+        <v>81</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>16660235</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16660235</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>아크아띠브 헤어룸</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>acattive_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학안로6번길 25</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/acattive_official</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>5</v>
+      </c>
+      <c r="R326" t="n">
+        <v>136</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>1730593492</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1730593492</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>나이스컷</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>varocoffee@naver.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>032-551-2384</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학동로 21</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>0</v>
+      </c>
+      <c r="R327" t="n">
+        <v>86</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>1072853009</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1072853009</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>코코헤어</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>032-555-5719</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 경명대로 1147</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>0</v>
+      </c>
+      <c r="R328" t="n">
+        <v>25</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>38365821</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38365821</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>아우라헤어</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>endal1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>032-549-4486</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 효서로 212 1층</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>0</v>
+      </c>
+      <c r="R329" t="n">
+        <v>303</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>37572830</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37572830</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>신사컷트</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>shp00304@naver.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학안로6번길 25</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>0</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>1163517307</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1163517307</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>다비치헤어</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0507-1352-6810</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 당미길 10 1F 다비치헤어</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>2</v>
+      </c>
+      <c r="R331" t="n">
+        <v>66</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>38387811</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38387811</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>염색살롱</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>ms1224@naver.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>032-555-5886</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 동양로 11 박촌동 풍림아이원 상가 염색살롱</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>2</v>
+      </c>
+      <c r="R332" t="n">
+        <v>90</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>1534956055</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1534956055</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>헤어스토리</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>jbjoo0537@naver.com</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>032-554-5354</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 황어로134번길 11</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>0</v>
+      </c>
+      <c r="R333" t="n">
+        <v>2</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>38382815</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38382815</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>머리예술</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>abirdcage@naver.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>032-544-9362</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 새벌로 126</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>1</v>
+      </c>
+      <c r="R334" t="n">
+        <v>47</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>19547403</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19547403</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Two mens hair salon</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>pseung1818@naver.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0507-1307-7579</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 계산로 83</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/two_mens_hairsalon</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>3</v>
+      </c>
+      <c r="R335" t="n">
+        <v>269</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>1034206899</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034206899</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>손문주 헤어샵</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 새벌로 89 (효성동 성지아파트 상가동 201</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>2</v>
+      </c>
+      <c r="R336" t="n">
+        <v>41</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>1985448316</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1985448316</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>와니살롱</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>foops80@naver.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>0507-1447-9091</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 계산천동로19번길 20 1층 와니살롱</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>1</v>
+      </c>
+      <c r="R337" t="n">
+        <v>136</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>1430887659</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1430887659</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>헤어 이루다</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>iruda1239@naver.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>0507-1328-1289</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 효서로 344 경민메디컬프라자 103호</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hair_2ruda</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>386</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>0</v>
+      </c>
+      <c r="R338" t="n">
+        <v>386</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>1240328147</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1240328147</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>숙미용실</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>ramgeys@naver.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 서운로 33-10</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>0</v>
+      </c>
+      <c r="R339" t="n">
+        <v>0</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>1836071911</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1836071911</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>비비 헤어</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>032-548-3330</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 계양산로 196</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>2</v>
+      </c>
+      <c r="R340" t="n">
+        <v>7</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>1282654189</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282654189</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>나이스가이 인천동양점</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>jungwoo4094600@naver.com</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>070-4232-1099</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 당미1길 7</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>http://www.iniceguy.com/</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>0</v>
+      </c>
+      <c r="R341" t="n">
+        <v>185</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>38557678</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38557678</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>프롬엘</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>tjd16@naver.com</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 황어로126번길 3</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>1</v>
+      </c>
+      <c r="R342" t="n">
+        <v>20</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>38381633</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38381633</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>핑크헤어컬렉션</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>gonggamyukyeong@naver.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>032-545-9695</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학서로24번길 5-1</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>0</v>
+      </c>
+      <c r="R343" t="n">
+        <v>13</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>1885711425</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1885711425</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>로아헤어</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>alswjddldi23@naver.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>0507-1327-5172</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 장제로 876 서해상가 2층 217호</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/alswjddldi23</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>881</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>1</v>
+      </c>
+      <c r="R344" t="n">
+        <v>882</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>1156551248</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1156551248</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>미미네애견미용실</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>miminepetshop@naver.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>0507-1341-9852</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 황어로126번길 14 102호</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xiPxfxbK</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>65</v>
+      </c>
+      <c r="R345" t="n">
+        <v>110</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>1664163010</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1664163010</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>스타일헤어</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>alla7390@naver.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>032-546-2487</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 장제로 876</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>0</v>
+      </c>
+      <c r="R346" t="n">
+        <v>22</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>1049058597</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1049058597</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>양림머리가꿈터</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>townspot@naver.com</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>032-544-0852</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 새벌로 112</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>2</v>
+      </c>
+      <c r="R347" t="n">
+        <v>64</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>1534877674</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1534877674</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>김컷트컷트</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>032-543-9884</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학안로 35 A-101(임학동,한솔파크빌)</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>0</v>
+      </c>
+      <c r="R348" t="n">
+        <v>116</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>16655322</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16655322</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>한진미용실</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>seu8511@naver.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>032-547-7335</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 병방로 28</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>0</v>
+      </c>
+      <c r="R349" t="n">
+        <v>13</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>21478591</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21478591</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>고은헤어</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>032-555-3007</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 새벌로 130 1층 고은헤어</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>1</v>
+      </c>
+      <c r="R350" t="n">
+        <v>78</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>1158362342</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1158362342</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>프리미엄 헤어살롱 미르</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>jaehyun0903@naver.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>0507-1430-6066</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 새벌로 112 마스터즈상가 1층 135, 136호</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jaehyun0903</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>1233</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>5</v>
+      </c>
+      <c r="R351" t="n">
+        <v>1238</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>1064824077</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1064824077</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>타임플러스계산지구점</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>tuesdaycherry@naver.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>032-542-5574</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 용종로 14</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>1</v>
+      </c>
+      <c r="R352" t="n">
+        <v>259</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>16933197</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16933197</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>미플러스헤어</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>thfhddl420@naver.com</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>032-563-5383</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 길마로 82 미플러스헤어</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://ok114.co.kr/0325635383</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>2</v>
+      </c>
+      <c r="R353" t="n">
+        <v>49</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>38388392</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38388392</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>엣지헤어</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>032-545-7982</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 양지로 144</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>2</v>
+      </c>
+      <c r="R354" t="n">
+        <v>74</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>37913614</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37913614</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>이은헤어</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>ok00urb@naver.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학서로6번길 13</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>0</v>
+      </c>
+      <c r="R355" t="n">
+        <v>27</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>38370788</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38370788</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>머리염색</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>오땡큐 임학점</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>malia98@naver.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>032-221-7672</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학서로27번길 1 1층</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
+        <v>58</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>1238483300</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1238483300</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>머리염색</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>구피염색방계산점</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>032-546-5040</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 계산시장길 21 1층</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>28</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>33253220</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33253220</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>땡글하개</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>dde_ngle@naver.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>0507-1390-7630</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 안남로519번길 4 101동 상가1층 106호</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dde_ngle</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>15</v>
+      </c>
+      <c r="R358" t="n">
+        <v>30</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>1276697582</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1276697582</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>온댕</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>ondangg@naver.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>0507-1446-7832</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 주부토로 426</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/l_on_daeng</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>17</v>
+      </c>
+      <c r="R359" t="n">
+        <v>42</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>1908396752</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1908396752</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>도그의 품격</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>adp4929@naver.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>0507-1360-2840</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 안남로554번길 8 1층</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>1</v>
+      </c>
+      <c r="R360" t="n">
+        <v>28</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>1783582750</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1783582750</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>아우어패밀리 인천본점</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>0507-1482-0105</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 경명대로1045번길 9-9 지산상가 202호 아우어패밀리</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ourfamily._official</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>24</v>
+      </c>
+      <c r="R361" t="n">
+        <v>56</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>1425555513</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1425555513</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>우리동네펫샵</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>0131miae@naver.com</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>0507-1361-1358</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 용종로 98-1 106호 우리동네펫샵</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/0131miae</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>312</v>
+      </c>
+      <c r="R362" t="n">
+        <v>423</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>1050496582</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1050496582</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>어스펫 1호점</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>funjin12@naver.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 장기로 24 102호 어스펫 1호점</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/funjin12</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>257</v>
+      </c>
+      <c r="R363" t="n">
+        <v>294</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>1776469821</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1776469821</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>아스타 펫 살롱</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>giyang1951@naver.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>0507-1381-1983</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 새벌로 140 1층</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>http://instagram.com/aster_pet_salon</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>7</v>
+      </c>
+      <c r="R364" t="n">
+        <v>44</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>1548645447</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1548645447</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>개예쁨주의</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>giyang1951@naver.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>0507-1349-7076</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 장제로997번길 5 1층 102호(박촌동)</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sj666_1</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>4</v>
+      </c>
+      <c r="R365" t="n">
+        <v>40</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>1131203259</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1131203259</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>개팔자상팔자 작전점</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>dran77@naver.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>0507-1349-1179</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 효서로 293 1층</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>http://instagram.com/simyangsu3</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>17</v>
+      </c>
+      <c r="R366" t="n">
+        <v>57</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>37765887</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37765887</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>엄댕샵</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>jyje0710@naver.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 아나지로307번길 14 1층 엄댕샵</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eomdang_shop/</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>3</v>
+      </c>
+      <c r="R367" t="n">
+        <v>39</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>1829617868</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1829617868</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>개냥아치</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>ojhj1022@naver.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>0507-1352-6270</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 계양산로 161 1층 개냥아치</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>3</v>
+      </c>
+      <c r="R368" t="n">
+        <v>33</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>1874800081</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874800081</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>비디코리아</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>bdkorea21@naver.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>032-676-2407</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 서운산단로8길 20 비디코리아</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bdkorea21</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>54</v>
+      </c>
+      <c r="R369" t="n">
+        <v>55</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>11644207</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11644207</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>으뜸이용원</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 양지로 49</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>1</v>
+      </c>
+      <c r="R370" t="n">
+        <v>5</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>21489631</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21489631</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>동양이발관</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>taekstory@naver.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 당미1길 25</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>0</v>
+      </c>
+      <c r="R371" t="n">
+        <v>16</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>1089780290</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089780290</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>학고을이발관</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>timmy0326@naver.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>032-517-9891</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 황어로126번길 20</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>1</v>
+      </c>
+      <c r="R372" t="n">
+        <v>1</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>38367077</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38367077</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>박촌이발</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>dashin2006@naver.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 장제로 1014</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>0</v>
+      </c>
+      <c r="R373" t="n">
+        <v>2</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>1489911278</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1489911278</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>시대이용원</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>sacheoncity@naver.com</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>032-542-6377</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학서로 22</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>0</v>
+      </c>
+      <c r="R374" t="n">
+        <v>5</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>19406831</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19406831</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>열린시각이용원</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>hnewskr@naver.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>032-512-3140</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 황어로115번길 10 신동아아파트 상가 105호</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>0</v>
+      </c>
+      <c r="R375" t="n">
+        <v>254</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>1584803012</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1584803012</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>애영이용원</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>swings81@naver.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>032-542-2882</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 임학동로56번길 16</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>0</v>
+      </c>
+      <c r="R376" t="n">
+        <v>0</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>38379600</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38379600</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>모조바버샵</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ssmnc@naver.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>0507-1326-4961</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 아나지로 332 카이저팰리스 101동상가116호 (인천광역시 계양구 작전동 392-1 카이저팰리스 101동상가 1층116호)</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
         <v>898</v>
       </c>
-      <c r="Q322" t="n">
+      <c r="Q377" t="n">
         <v>4</v>
       </c>
-      <c r="R322" t="n">
+      <c r="R377" t="n">
         <v>902</v>
       </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T322" t="inlineStr">
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
         <is>
           <t>1162828726</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="U377" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1162828726</t>
         </is>
       </c>
-      <c r="V322" t="inlineStr">
+      <c r="V377" t="inlineStr">
         <is>
           <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>구일이용원</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 계양산로215번길 20</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>0</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>19404004</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19404004</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
